--- a/samples/mapping/invoice/template.xlsx
+++ b/samples/mapping/invoice/template.xlsx
@@ -729,9 +729,10 @@
           <t>**@item.price</t>
         </is>
       </c>
-      <c r="F10" s="12">
-        <f>D10*E10</f>
-        <v/>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>**@item.lineTotal</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
